--- a/public/templates/Brandzo-Items-Template.xlsx
+++ b/public/templates/Brandzo-Items-Template.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
-    <sheet name="تعليمات" sheetId="2" r:id="rId2"/>
+    <sheet name="Balances" sheetId="2" r:id="rId2"/>
+    <sheet name="تعليمات" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -458,7 +459,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="1" t="str">
         <v/>
       </c>
       <c r="B2" t="str">
@@ -507,11 +508,91 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:I2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Bar Code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Item Code (كود الصنف)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Item Description (اسم الصنف)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Warehouse (المخزن)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Location (الموقع/الرف)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Batch / Lot (التشغيلة)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Expiry (تاريخ الصلاحية)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Qty (الكمية)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Count Date (تاريخ الرصيد)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="str">
+        <v>8059692040599</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>مثال — احذف هذا الصف</v>
+      </c>
+      <c r="D2" t="str">
+        <v>E5</v>
+      </c>
+      <c r="E2" t="str">
+        <v>A-01-3</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v>LOT-2026-11</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2027-03-31</v>
+      </c>
+      <c r="H2">
+        <v>24</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-07-15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C39"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="78.83203125" customWidth="1"/>
+    <col min="3" max="3" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,214 +602,342 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>العمود</v>
-      </c>
-      <c r="B3" t="str">
-        <v>إلزامي؟</v>
-      </c>
-      <c r="C3" t="str">
-        <v>الشرح</v>
+        <v>الملف ورقتان: «Items» تعريف الأصناف (يتغيّر نادرًا) · «Balances» الأرصدة (تتغيّر يوميًّا).</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Item Code (كود الصنف)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>لا</v>
-      </c>
-      <c r="C4" t="str">
-        <v>اتركه فارغًا الآن — حاوية محجوزة تُملأ من أودو يوم الربط. هوية الصنف لا تعتمد عليه، فلا ينكسر شيء حين يصل.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Item Description (اسم الصنف)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>نعم</v>
-      </c>
-      <c r="C5" t="str">
-        <v>إلزامي. اسم الصنف كما يظهر في المستندات المطبوعة.</v>
+        <v>ارفع أيّهما وحدها — رفع التعريفات لا يمسّ الأرصدة أبدًا، والعكس.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Bar Code</v>
+        <v>── ورقة Items ──</v>
       </c>
       <c r="B6" t="str">
-        <v>لا</v>
+        <v>إلزامي؟</v>
       </c>
       <c r="C6" t="str">
-        <v>الباركود الرئيسي. اتركه فارغًا فقط إن كان الكود موجودًا.</v>
+        <v>الشرح</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bar Code - Code</v>
+        <v>Item Code (كود الصنف)</v>
       </c>
       <c r="B7" t="str">
         <v>لا</v>
       </c>
       <c r="C7" t="str">
-        <v>باركود إضافي لنفس الصنف (عبوة أخرى أو مورّد آخر) — يُضمّ مع الأول لا يستبدله.</v>
+        <v>اتركه فارغًا الآن — حاوية محجوزة تُملأ من أودو يوم الربط. هوية الصنف لا تعتمد عليه، فلا ينكسر شيء حين يصل.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Purchase Price (سعر الشراء)</v>
+        <v>Item Description (اسم الصنف)</v>
       </c>
       <c r="B8" t="str">
-        <v>لا</v>
+        <v>نعم</v>
       </c>
       <c r="C8" t="str">
-        <v>سعر الشراء (التكلفة). بالدينار الليبي.</v>
+        <v>إلزامي في ورقة Items. اسم الصنف كما يظهر في المستندات المطبوعة.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sell Price (سعر البيع)</v>
+        <v>Bar Code</v>
       </c>
       <c r="B9" t="str">
         <v>لا</v>
       </c>
       <c r="C9" t="str">
-        <v>سعر البيع. لا تخلطه بسعر الشراء.</v>
+        <v>الباركود الرئيسي. اتركه فارغًا فقط إن كان الكود موجودًا.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>UoM Group Code</v>
+        <v>Bar Code - Code</v>
       </c>
       <c r="B10" t="str">
         <v>لا</v>
       </c>
       <c r="C10" t="str">
-        <v>كود مجموعة الوحدة (مثل PCS).</v>
+        <v>باركود إضافي لنفس الصنف (عبوة أخرى أو مورّد آخر) — يُضمّ مع الأول لا يستبدله.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>UoM Group Name</v>
+        <v>Purchase Price (سعر الشراء)</v>
       </c>
       <c r="B11" t="str">
         <v>لا</v>
       </c>
       <c r="C11" t="str">
-        <v>اسم مجموعة الوحدة (قطعة · كرتون · علبة …).</v>
+        <v>سعر الشراء (التكلفة). بالدينار الليبي.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Department (القسم)</v>
+        <v>Sell Price (سعر البيع)</v>
       </c>
       <c r="B12" t="str">
         <v>لا</v>
       </c>
       <c r="C12" t="str">
-        <v>المستوى الأول من التصنيف.</v>
+        <v>سعر البيع. لا تخلطه بسعر الشراء.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Section (الشعبة)</v>
+        <v>UoM Group Code</v>
       </c>
       <c r="B13" t="str">
         <v>لا</v>
       </c>
       <c r="C13" t="str">
-        <v>المستوى الثاني.</v>
+        <v>كود مجموعة الوحدة (مثل PCS).</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Family (العائلة)</v>
+        <v>UoM Group Name</v>
       </c>
       <c r="B14" t="str">
         <v>لا</v>
       </c>
       <c r="C14" t="str">
-        <v>المستوى الثالث.</v>
+        <v>اسم مجموعة الوحدة (قطعة · كرتون · علبة …).</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Sub-Family (العائلة الفرعية)</v>
+        <v>Department (القسم)</v>
       </c>
       <c r="B15" t="str">
         <v>لا</v>
       </c>
       <c r="C15" t="str">
-        <v>المستوى الرابع (الأدقّ).</v>
+        <v>المستوى الأول من التصنيف.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>المورد</v>
+        <v>Section (الشعبة)</v>
       </c>
       <c r="B16" t="str">
         <v>لا</v>
       </c>
       <c r="C16" t="str">
-        <v>اسم المورّد الرئيسي للصنف.</v>
+        <v>المستوى الثاني.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Family (العائلة)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C17" t="str">
+        <v>المستوى الثالث.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>قواعد عامة:</v>
+        <v>Sub-Family (العائلة الفرعية)</v>
+      </c>
+      <c r="B18" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C18" t="str">
+        <v>المستوى الرابع (الأدقّ).</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>١</v>
+        <v>المورد</v>
       </c>
       <c r="B19" t="str">
-        <v>لا تحذف صفّ العناوين ولا تغيّر أسماء الأعمدة — النظام يتعرّف عليها.</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>٢</v>
-      </c>
-      <c r="B20" t="str">
-        <v>الصفّ الذي لا يحمل كودًا ولا باركودًا يُرفض: لا سبيل للتعرّف عليه.</v>
+        <v>لا</v>
+      </c>
+      <c r="C19" t="str">
+        <v>اسم المورّد الرئيسي للصنف.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>٣</v>
+        <v>── ورقة Balances ──</v>
       </c>
       <c r="B21" t="str">
-        <v>الصنف ذو الباركودات المتعدّدة: كرّر صفّه، أو افصل الباركودات بفاصلة في الخانة نفسها.</v>
+        <v>إلزامي؟</v>
+      </c>
+      <c r="C21" t="str">
+        <v>الشرح</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>٤</v>
+        <v>Bar Code</v>
       </c>
       <c r="B22" t="str">
-        <v>اجعل خانات الباركود **نصًّا** (Format → Text) قبل اللصق، وإلا حوّلها إكسيل إلى 8.05969E+12 وأفسدها.</v>
+        <v>لا</v>
+      </c>
+      <c r="C22" t="str">
+        <v>الباركود الرئيسي. اتركه فارغًا فقط إن كان الكود موجودًا.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>٥</v>
+        <v>Item Code (كود الصنف)</v>
       </c>
       <c r="B23" t="str">
-        <v>إعادة الرفع تُحدّث ولا تُكرّر، والباركودات تُضمّ ولا تُمحى. والأعمدة الغائبة لا تُفرِّغ بيانات قائمة.</v>
+        <v>لا</v>
+      </c>
+      <c r="C23" t="str">
+        <v>اتركه فارغًا الآن — حاوية محجوزة تُملأ من أودو يوم الربط. هوية الصنف لا تعتمد عليه، فلا ينكسر شيء حين يصل.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>Item Description (اسم الصنف)</v>
+      </c>
+      <c r="B24" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C24" t="str">
+        <v>إلزامي في ورقة Items. اسم الصنف كما يظهر في المستندات المطبوعة.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Warehouse (المخزن)</v>
+      </c>
+      <c r="B25" t="str">
+        <v>نعم</v>
+      </c>
+      <c r="C25" t="str">
+        <v>إلزامي في ورقة Balances. المخزن: E5 · E2 · E3. الصنف يتكرّر بعدد مخازنه.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Location (الموقع/الرف)</v>
+      </c>
+      <c r="B26" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C26" t="str">
+        <v>الرفّ أو البوكس داخل المخزن (اختياري — لمن انضبط ترقيم أرففه).</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Batch / Lot (التشغيلة)</v>
+      </c>
+      <c r="B27" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C27" t="str">
+        <v>رقم التشغيلة. تشغيلتان لنفس الصنف = صفّان، لكلٍّ صلاحيته.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Expiry (تاريخ الصلاحية)</v>
+      </c>
+      <c r="B28" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C28" t="str">
+        <v>تاريخ الصلاحية (YYYY-MM-DD). ★ عليه يقوم حارس FEFO وتنبيه قرب الانتهاء.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Qty (الكمية)</v>
+      </c>
+      <c r="B29" t="str">
+        <v>نعم</v>
+      </c>
+      <c r="C29" t="str">
+        <v>إلزامي. الكمية. **الصفر رقم مشروع** ويعني «نفد من هذا المخزن» — لا تحذف الصف.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Count Date (تاريخ الرصيد)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C30" t="str">
+        <v>تاريخ صحّة هذا الرصيد (يوم الجرد أو تصدير التقرير).</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>قواعد عامة:</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>١</v>
+      </c>
+      <c r="B33" t="str">
+        <v>لا تحذف صفّ العناوين ولا تغيّر أسماء الأعمدة — النظام يتعرّف عليها.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>٢</v>
+      </c>
+      <c r="B34" t="str">
+        <v>صفٌّ بلا كود وبلا باركود يُرفض: لا سبيل للتعرّف عليه.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>٣</v>
+      </c>
+      <c r="B35" t="str">
+        <v>الصنف ذو الباركودات المتعدّدة: كرّر صفّه، أو افصل الباركودات بفاصلة في الخانة نفسها.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>٤</v>
+      </c>
+      <c r="B36" t="str">
+        <v>اجعل خانات الباركود **نصًّا** (Format → Text) قبل اللصق، وإلا حوّلها إكسيل إلى 8.05969E+12 وأفسدها.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>٥</v>
+      </c>
+      <c r="B37" t="str">
+        <v>في Balances: الصنف يتكرّر بعدد (المخزن × التشغيلة) — هذا مقصود لا خطأ.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
         <v>٦</v>
       </c>
-      <c r="B24" t="str">
-        <v>الاستيراد يعرض لك معاينة بما سيتغيّر قبل الحفظ — راجعها.</v>
+      <c r="B38" t="str">
+        <v>إعادة الرفع تُحدّث ولا تُكرّر، والباركودات تُضمّ ولا تُمحى. والأعمدة الغائبة لا تُفرِّغ بيانات قائمة.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>٧</v>
+      </c>
+      <c r="B39" t="str">
+        <v>الاستيراد يعرض معاينة بما سيتغيّر قبل الحفظ — راجعها.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/Brandzo-Items-Template.xlsx
+++ b/public/templates/Brandzo-Items-Template.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:O2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -415,6 +415,8 @@
     <col min="11" max="11" width="18.83203125" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,6 +459,12 @@
       <c r="M1" t="str">
         <v>المورد</v>
       </c>
+      <c r="N1" t="str">
+        <v>Min Stock (الحد الأدنى)</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Status (الحالة)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
@@ -498,17 +506,23 @@
       <c r="M2" t="str">
         <v>اسم المورّد</v>
       </c>
+      <c r="N2">
+        <v>6</v>
+      </c>
+      <c r="O2" t="str">
+        <v>نشط</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -519,6 +533,7 @@
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,6 +562,9 @@
         <v>Qty (الكمية)</v>
       </c>
       <c r="I1" t="str">
+        <v>Unit Cost (تكلفة الوحدة)</v>
+      </c>
+      <c r="J1" t="str">
         <v>Count Date (تاريخ الرصيد)</v>
       </c>
     </row>
@@ -575,20 +593,23 @@
       <c r="H2">
         <v>24</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2">
+        <v>12.5</v>
+      </c>
+      <c r="J2" t="str">
         <v>2026-07-15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -764,180 +785,213 @@
         <v>اسم المورّد الرئيسي للصنف.</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Min Stock (الحد الأدنى)</v>
+      </c>
+      <c r="B20" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C20" t="str">
+        <v>حدّ إعادة الطلب. عليه يقوم تنبيه «المخزون المنخفض» في شاشة الأصناف — واتركه فارغًا فلا تنبيه.</v>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>── ورقة Balances ──</v>
+        <v>Status (الحالة)</v>
       </c>
       <c r="B21" t="str">
-        <v>إلزامي؟</v>
+        <v>لا</v>
       </c>
       <c r="C21" t="str">
-        <v>الشرح</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Bar Code</v>
-      </c>
-      <c r="B22" t="str">
-        <v>لا</v>
-      </c>
-      <c r="C22" t="str">
-        <v>الباركود الرئيسي. اتركه فارغًا فقط إن كان الكود موجودًا.</v>
+        <v>نشط (أو اتركه فارغًا) · موقوف = يُخفى من القوائم دون حذف. الفارغ يعني نشطًا.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Item Code (كود الصنف)</v>
+        <v>── ورقة Balances ──</v>
       </c>
       <c r="B23" t="str">
-        <v>لا</v>
+        <v>إلزامي؟</v>
       </c>
       <c r="C23" t="str">
-        <v>اتركه فارغًا الآن — حاوية محجوزة تُملأ من أودو يوم الربط. هوية الصنف لا تعتمد عليه، فلا ينكسر شيء حين يصل.</v>
+        <v>الشرح</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Item Description (اسم الصنف)</v>
+        <v>Bar Code</v>
       </c>
       <c r="B24" t="str">
         <v>لا</v>
       </c>
       <c r="C24" t="str">
-        <v>إلزامي في ورقة Items. اسم الصنف كما يظهر في المستندات المطبوعة.</v>
+        <v>الباركود الرئيسي. اتركه فارغًا فقط إن كان الكود موجودًا.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Warehouse (المخزن)</v>
+        <v>Item Code (كود الصنف)</v>
       </c>
       <c r="B25" t="str">
-        <v>نعم</v>
+        <v>لا</v>
       </c>
       <c r="C25" t="str">
-        <v>إلزامي في ورقة Balances. المخزن: E5 · E2 · E3. الصنف يتكرّر بعدد مخازنه.</v>
+        <v>اتركه فارغًا الآن — حاوية محجوزة تُملأ من أودو يوم الربط. هوية الصنف لا تعتمد عليه، فلا ينكسر شيء حين يصل.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Location (الموقع/الرف)</v>
+        <v>Item Description (اسم الصنف)</v>
       </c>
       <c r="B26" t="str">
         <v>لا</v>
       </c>
       <c r="C26" t="str">
-        <v>الرفّ أو البوكس داخل المخزن (اختياري — لمن انضبط ترقيم أرففه).</v>
+        <v>إلزامي في ورقة Items. اسم الصنف كما يظهر في المستندات المطبوعة.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Batch / Lot (التشغيلة)</v>
+        <v>Warehouse (المخزن)</v>
       </c>
       <c r="B27" t="str">
-        <v>لا</v>
+        <v>نعم</v>
       </c>
       <c r="C27" t="str">
-        <v>رقم التشغيلة. تشغيلتان لنفس الصنف = صفّان، لكلٍّ صلاحيته.</v>
+        <v>إلزامي في ورقة Balances. المخزن: E5 · E2 · E3. الصنف يتكرّر بعدد مخازنه.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Expiry (تاريخ الصلاحية)</v>
+        <v>Location (الموقع/الرف)</v>
       </c>
       <c r="B28" t="str">
         <v>لا</v>
       </c>
       <c r="C28" t="str">
-        <v>تاريخ الصلاحية (YYYY-MM-DD). ★ عليه يقوم حارس FEFO وتنبيه قرب الانتهاء.</v>
+        <v>الرفّ أو البوكس داخل المخزن (اختياري — لمن انضبط ترقيم أرففه).</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Qty (الكمية)</v>
+        <v>Batch / Lot (التشغيلة)</v>
       </c>
       <c r="B29" t="str">
-        <v>نعم</v>
+        <v>لا</v>
       </c>
       <c r="C29" t="str">
-        <v>إلزامي. الكمية. **الصفر رقم مشروع** ويعني «نفد من هذا المخزن» — لا تحذف الصف.</v>
+        <v>رقم التشغيلة. تشغيلتان لنفس الصنف = صفّان، لكلٍّ صلاحيته.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Count Date (تاريخ الرصيد)</v>
+        <v>Expiry (تاريخ الصلاحية)</v>
       </c>
       <c r="B30" t="str">
         <v>لا</v>
       </c>
       <c r="C30" t="str">
-        <v>تاريخ صحّة هذا الرصيد (يوم الجرد أو تصدير التقرير).</v>
+        <v>تاريخ الصلاحية (YYYY-MM-DD). ★ عليه يقوم حارس FEFO وتنبيه قرب الانتهاء.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Qty (الكمية)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>نعم</v>
+      </c>
+      <c r="C31" t="str">
+        <v>إلزامي. الكمية. **الصفر رقم مشروع** ويعني «نفد من هذا المخزن» — لا تحذف الصف.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>قواعد عامة:</v>
+        <v>Unit Cost (تكلفة الوحدة)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>لا</v>
+      </c>
+      <c r="C32" t="str">
+        <v>تكلفة الوحدة في **هذه التشغيلة** — لا سعر الشراء الحالي. عليها يقوم تقييم المخزون والإغلاق المالي.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>١</v>
+        <v>Count Date (تاريخ الرصيد)</v>
       </c>
       <c r="B33" t="str">
-        <v>لا تحذف صفّ العناوين ولا تغيّر أسماء الأعمدة — النظام يتعرّف عليها.</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>٢</v>
-      </c>
-      <c r="B34" t="str">
-        <v>صفٌّ بلا كود وبلا باركود يُرفض: لا سبيل للتعرّف عليه.</v>
+        <v>لا</v>
+      </c>
+      <c r="C33" t="str">
+        <v>تاريخ صحّة هذا الرصيد (يوم الجرد أو تصدير التقرير).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>٣</v>
-      </c>
-      <c r="B35" t="str">
-        <v>الصنف ذو الباركودات المتعدّدة: كرّر صفّه، أو افصل الباركودات بفاصلة في الخانة نفسها.</v>
+        <v>قواعد عامة:</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>٤</v>
+        <v>١</v>
       </c>
       <c r="B36" t="str">
-        <v>اجعل خانات الباركود **نصًّا** (Format → Text) قبل اللصق، وإلا حوّلها إكسيل إلى 8.05969E+12 وأفسدها.</v>
+        <v>لا تحذف صفّ العناوين ولا تغيّر أسماء الأعمدة — النظام يتعرّف عليها.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>٥</v>
+        <v>٢</v>
       </c>
       <c r="B37" t="str">
-        <v>في Balances: الصنف يتكرّر بعدد (المخزن × التشغيلة) — هذا مقصود لا خطأ.</v>
+        <v>صفٌّ بلا كود وبلا باركود يُرفض: لا سبيل للتعرّف عليه.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>٦</v>
+        <v>٣</v>
       </c>
       <c r="B38" t="str">
-        <v>إعادة الرفع تُحدّث ولا تُكرّر، والباركودات تُضمّ ولا تُمحى. والأعمدة الغائبة لا تُفرِّغ بيانات قائمة.</v>
+        <v>الصنف ذو الباركودات المتعدّدة: كرّر صفّه، أو افصل الباركودات بفاصلة في الخانة نفسها.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v>٤</v>
+      </c>
+      <c r="B39" t="str">
+        <v>اجعل خانات الباركود **نصًّا** (Format → Text) قبل اللصق، وإلا حوّلها إكسيل إلى 8.05969E+12 وأفسدها.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>٥</v>
+      </c>
+      <c r="B40" t="str">
+        <v>في Balances: الصنف يتكرّر بعدد (المخزن × التشغيلة) — هذا مقصود لا خطأ.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>٦</v>
+      </c>
+      <c r="B41" t="str">
+        <v>إعادة الرفع تُحدّث ولا تُكرّر، والباركودات تُضمّ ولا تُمحى. والأعمدة الغائبة لا تُفرِّغ بيانات قائمة.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
         <v>٧</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B42" t="str">
         <v>الاستيراد يعرض معاينة بما سيتغيّر قبل الحفظ — راجعها.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
   </ignoredErrors>
 </worksheet>
 </file>